--- a/光伏配储项目/电价数据/2026/紫洞站.xlsx
+++ b/光伏配储项目/电价数据/2026/紫洞站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51156</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.76395</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57484</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.60523</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.52146</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.51973</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45446</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44447</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42371</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42258</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40902</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42315</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38497</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41332</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44448</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26835</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.13144</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10675</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.12265</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.11243</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13553</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.05039</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11291</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.16577</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.15341</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.09598000000000001</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09164</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01812</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10406</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.04031000000000001</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15366</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21729</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25877</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23426</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24711</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.11351</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.25624</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14485</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28695</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21697</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6660199999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5597300000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.58801</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.38964</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.41327</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.6311599999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.46816</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44765</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.44099</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.58186</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.48274</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6460900000000001</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.83068</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.64363</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6594</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.81355</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.22634</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43344</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6952999999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6033999999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.8568600000000001</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.65885</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.6689299999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6579199999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.62866</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.48079</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48064</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41615</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42582</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71333</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76612</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7963300000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.53002</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8539099999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53512</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51842</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5051100000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51088</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48819</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40303</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46964</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39072</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41864</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.60073</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.74234</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42897</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.43968</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43801</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.52644</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.17858</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06968000000000001</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41409</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50964</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7714099999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.24157</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.43718</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.81396</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.5425599999999999</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.14389</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.5265299999999999</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.26838</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.28533</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.43884</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.43901</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.65683</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.80077</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.6452599999999999</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.7016100000000001</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.79016</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.74571</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.68416</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.61027</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77678</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.59741</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.46096</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.06556</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.4753</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.66769</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44446</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43792</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42378</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3346</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5172899999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38311</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.53774</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.42979</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40505</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.42005</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43798</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45469</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39619</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45455</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44881</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.48954</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.39451</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.22477</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.5112300000000001</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26981</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.48036</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.41146</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.52037</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49253</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.17169</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.28882</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28584</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40692</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.41458</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5279400000000001</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.41751</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5081</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.61863</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5762</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.64974</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7548899999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.57568</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.50843</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45102</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.54174</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.49473</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45654</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47801</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.46383</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44769</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.42447</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41393</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34238</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.40675</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.43349</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46075</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.28167</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.22486</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.22601</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.18555</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.26924</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.52673</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45466</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.10631</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.17801</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28845</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.19093</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.23677</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.5382899999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07346999999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.13271</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.24159</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.25413</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.21936</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.23837</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.20328</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26711</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.12254</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.26332</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.27094</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39619</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.44105</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.66186</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.4709</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.4324</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29994</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27854</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25929</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04024</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.05234</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.05403</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04458</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04202</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04790999999999999</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04346</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03592</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04701</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04797999999999999</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04632</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04536</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04573</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04739</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.0442</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04654999999999999</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04336</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04191</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.0444</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04557</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21823</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04074000000000001</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04659000000000001</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05522999999999999</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04974</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04745000000000001</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00389</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.01991</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15926</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.11562</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37658</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40928</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46735</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39625</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41647</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35064</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6808500000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.3996499999999999</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44506</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4223</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42219</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10256</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.0438</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04695000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04616</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04616</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04616</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04557</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04391</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04602000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09923</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00398</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04383</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04391</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04573</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04559000000000001</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04555</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04355</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04325</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04611</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04415</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04807</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04979</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04454</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04728</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04768</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20004</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14293</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33546</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31768</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40438</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28815</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27131</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2711</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17249</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15874</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17103</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14778</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15952</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15868</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23628</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21409</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22665</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26886</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28586</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28062</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27208</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42845</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45588</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41852</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41542</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15629</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50775</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79092</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62209</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49806</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810900000000001</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.9205599999999999</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49468</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9157000000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86648</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29869</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89164</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63247</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19121</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8708400000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5415399999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.335</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03581</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53487</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79437</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5295700000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7764</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78024</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87719</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87564</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49633</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40403</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4536</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21113</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87902</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55114</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6259600000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53937</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49891</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45637</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43792</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45018</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42008</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41463</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43358</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40332</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5857</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5957</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60181</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66275</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.4752</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41943</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58243</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4524</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88061</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63139</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8802300000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.86277</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8660599999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44403</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.46916</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41208</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45161</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41442</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35329</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9191</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46479</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46581</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40933</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49901</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29103</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16642</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26272</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19902</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19403</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2785899999999999</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2557</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27845</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27645</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43214</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.4477</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4199</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.595</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88998</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.33153</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.1388</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69841</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78874</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64474</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5778099999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44891</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43951</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43675</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41467</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42287</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49926</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41259</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43371</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41215</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43374</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44932</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43316</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41259</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41262</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42258</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39564</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49445</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.16257</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.63248</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.40506</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25048</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.17969</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.69936</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.43469</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.7990499999999999</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.42337</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26291</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26155</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37565</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5781799999999999</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46195</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.75062</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46396</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43655</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.41983</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32347</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.37121</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.17069</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.17617</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>1.18306</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.15243</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>1.16513</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>1.15262</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>1.16347</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.28855</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>1.16824</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>1.29732</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>1.16249</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.23241</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>1.13541</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>1.13768</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>1.21319</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16162</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.45347</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.42772</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44834</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.41745</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44052</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43835</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43769</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44259</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44347</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40182</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34842</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5367999999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46713</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42256</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41468</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28206</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26548</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20284</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24957</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24259</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.26311</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27638</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2413</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.2931</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28485</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24241</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.45994</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35983</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41584</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41647</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.4416600000000001</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.50534</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44187</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.88581</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.67332</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24962</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.8336399999999999</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.12627</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43652</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.42285</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42604</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70888</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.53303</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.25936</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.2847</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34941</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65211</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7736000000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45094</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45745</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34368</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41024</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.4248</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28552</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28499</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20139</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26263</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28031</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22434</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.28007</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28602</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28159</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.91688</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.81778</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.81253</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.57296</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.8145</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.8021900000000001</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36822</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43919</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42434</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64808</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60538</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.58401</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46534</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.67238</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.4632</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.82529</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43213</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.07304</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40806</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47657</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42964</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41764</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35977</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48956</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.53837</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4852</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49429</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39682</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40921</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40727</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41547</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40956</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4079700000000001</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38964</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41139</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44903</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44714</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5575399999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49882</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44937</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47502</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41995</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44928</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.50928</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.6726799999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.46801</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40976</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.4064</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42021</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6551699999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.23748</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.38423</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42134</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.4416</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49377</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43996</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.51062</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.51058</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5450199999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6956599999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7287</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.67298</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.81191</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.59249</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52389</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8307899999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77083</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62818</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67495</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45024</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.48053</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48191</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47655</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.4679700000000001</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41721</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55657</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44129</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45479</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42417</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44481</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45357</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40434</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39551</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38624</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.21087</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39599</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04799</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40362</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46174</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11897</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18022</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.38629</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38254</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>1.05829</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43084</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43577</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40824</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3957</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36473</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.2263</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23089</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29085</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25069</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13923</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25438</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04301</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25094</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17182</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18376</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.28734</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22927</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24987</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26865</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23271</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27574</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28433</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34943</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28806</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25174</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23729</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16322</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20178</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.25069</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01851</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00122</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.03069</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04882</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11472</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01882</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03879999999999999</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04885</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.00787</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03348</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04654999999999999</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04581</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02236</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.01865</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04891</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.18884</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04886</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04889</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04893</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0487</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04888</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03369</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04884</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04847</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04288</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18347</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.19255</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23282</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28064</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26147</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26312</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.2595</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26663</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28534</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41094</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28948</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28697</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28162</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.27987</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.12442</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.56435</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.14577</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28468</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.27556</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25369</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.26406</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.22904</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25776</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.24759</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.2121</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.23776</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.24018</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.26233</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.26225</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24267</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29682</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.26821</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27221</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.27404</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.21865</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.14294</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.62873</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.6053200000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.6452599999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.57963</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.15768</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11706</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23558</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17723</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.10684</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.11686</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.06808</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22563</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.0994</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.01534</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.03034</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.0895</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.16888</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02752</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.10812</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.1188</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.13787</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.02226</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.09026999999999999</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.10409</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.10228</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.14175</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.26068</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37827</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32303</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.57589</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.55865</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.43829</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.45583</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.4798</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45081</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.45148</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14275</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.28058</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27028</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28057</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.50354</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40789</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32831</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.27889</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.6267699999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5891900000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.51108</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.44942</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26436</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28726</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49643</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.50662</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46941</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.48929</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42773</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.6245000000000001</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.42319</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4418</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.4987799999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41572</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45528</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40454</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.14704</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36755</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48194</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39593</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37815</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37374</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.42112</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39564</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3898</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.47391</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38437</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37369</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27879</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.36446</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.5591900000000001</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.43157</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.5178400000000001</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.46964</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.44017</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51571</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5833700000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.58668</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.4251</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5275</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5107699999999999</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.55353</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.4733</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.51891</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.42892</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.69917</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8670800000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.58399</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.58347</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44195</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37235</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.25744</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.22869</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.18265</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.16292</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07614</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.44898</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.23082</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.22153</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.17697</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01191</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26723</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.17348</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06628000000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06048</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.08084999999999999</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17825</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08817</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.06322999999999999</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.18015</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.16267</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.23269</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.25062</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42965</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40811</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41637</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42828</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42581</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38315</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35959</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8655700000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.47065</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42506</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39522</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.26366</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24952</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11441</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.25789</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.27707</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.39776</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.42739</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.7722100000000001</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00393</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01938</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04863</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02031</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02573</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.26009</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04844</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23837</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.10034</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>1.09848</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.28637</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.32095</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.34756</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.33456</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.49867</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.4293</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.42022</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.58052</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.41227</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35929</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.61529</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.4552</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28023</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25787</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23022</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14395</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20579</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22939</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23118</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1142</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15021</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04727000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04737</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04658</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04734</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04689</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07851999999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03005</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06304</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09675</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17026</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19582</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12044</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.25467</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22945</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12401</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05534</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26235</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14628</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11733</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23657</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18494</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23632</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.24321</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20324</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24392</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.27385</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39023</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46719</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38899</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36599</v>
       </c>
     </row>
   </sheetData>
